--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.81943994326521</v>
+        <v>10.0456589907806</v>
       </c>
       <c r="D2" t="n">
-        <v>13.64734406395618</v>
+        <v>2.217693410392879</v>
       </c>
       <c r="E2" t="n">
-        <v>16.90458030702206</v>
+        <v>2.746994299891084</v>
       </c>
       <c r="F2" t="n">
-        <v>7.003275992597583</v>
+        <v>1.138032348797107</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39526688614011</v>
+        <v>3.314230868997768</v>
       </c>
       <c r="D3" t="n">
-        <v>20.08887064043078</v>
+        <v>3.264441479070002</v>
       </c>
       <c r="E3" t="n">
-        <v>16.90458030702206</v>
+        <v>2.746994299891084</v>
       </c>
       <c r="F3" t="n">
-        <v>7.003275992597583</v>
+        <v>1.138032348797107</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.22757874798577</v>
+        <v>7.186981546547688</v>
       </c>
       <c r="D4" t="n">
-        <v>15.57241150239744</v>
+        <v>2.530516869139583</v>
       </c>
       <c r="E4" t="n">
-        <v>16.90458030702206</v>
+        <v>2.746994299891084</v>
       </c>
       <c r="F4" t="n">
-        <v>7.003275992597583</v>
+        <v>1.138032348797107</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.67005594865195</v>
+        <v>2.871384091655942</v>
       </c>
       <c r="D5" t="n">
-        <v>5.572138543326098</v>
+        <v>0.9054725132904909</v>
       </c>
       <c r="E5" t="n">
-        <v>16.90458030702206</v>
+        <v>2.746994299891084</v>
       </c>
       <c r="F5" t="n">
-        <v>7.003275992597583</v>
+        <v>1.138032348797107</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.01746904054829</v>
+        <v>7.802838719089098</v>
       </c>
       <c r="D6" t="n">
-        <v>26.70299262239372</v>
+        <v>4.339236301138979</v>
       </c>
       <c r="E6" t="n">
-        <v>16.90458030702206</v>
+        <v>2.746994299891084</v>
       </c>
       <c r="F6" t="n">
-        <v>7.003275992597583</v>
+        <v>1.138032348797107</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
